--- a/safety_inspection_forms/019_oil_rig_safety_inspection_form--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/019_oil_rig_safety_inspection_form--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Equipment Inspections Comments</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Safety Equipment Testing Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Personnel Inspections Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Fire Prevention Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Fire Fighting Equipment Comments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Emergency Exit Routes Comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Electrical Systems Comments</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Electrical Equipment Testing Comments</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Electrical Inspections Comments</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Gas Systems Comments</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Gas Equipment Testing Comments</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>equipment_inspections_choices</t>
+          <t>general_inspections_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,318 +1182,505 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>safety_equipment_testing_choices</t>
+          <t>equipment_inspections_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>safety_equipment_testing_choices</t>
+          <t>equipment_inspections_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>personnel_inspections_choices</t>
+          <t>safety_equipment_testing_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>personnel_inspections_choices</t>
+          <t>safety_equipment_testing_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fire_fighting_equipment_choices</t>
+          <t>safety_equipment_testing_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fire_fighting_equipment_choices</t>
+          <t>personnel_inspections_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>emergency_exit_routes_choices</t>
+          <t>personnel_inspections_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>emergency_exit_routes_choices</t>
+          <t>personnel_inspections_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>electrical_systems_choices</t>
+          <t>fire_fighting_equipment_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>electrical_systems_choices</t>
+          <t>fire_fighting_equipment_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>electrical_equipment_testing_choices</t>
+          <t>fire_fighting_equipment_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>electrical_equipment_testing_choices</t>
+          <t>emergency_exit_routes_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>electrical_inspections_choices</t>
+          <t>emergency_exit_routes_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>electrical_inspections_choices</t>
+          <t>emergency_exit_routes_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gas_systems_choices</t>
+          <t>electrical_systems_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gas_systems_choices</t>
+          <t>electrical_systems_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gas_equipment_testing_choices</t>
+          <t>electrical_systems_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>electrical_equipment_testing_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>electrical_equipment_testing_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>electrical_equipment_testing_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>electrical_inspections_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>electrical_inspections_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>electrical_inspections_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>gas_systems_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>gas_systems_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>gas_systems_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>gas_equipment_testing_choices</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option2</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>gas_equipment_testing_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>gas_equipment_testing_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
